--- a/data/trans_dic/P36B02_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P36B02_R-Habitat-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>88,11%</t>
+          <t>88,18%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>90,65%</t>
+          <t>90,4%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>89,42%</t>
+          <t>89,32%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>93,18; 96,41</t>
+          <t>93,23; 96,47</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>93,03; 96,7</t>
+          <t>93,15; 96,51</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>90,41; 94,61</t>
+          <t>90,45; 94,64</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>84,96; 90,7</t>
+          <t>84,93; 90,56</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>93,61; 96,78</t>
+          <t>93,81; 96,91</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,83; 97,03</t>
+          <t>93,79; 97,04</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>93,75; 96,95</t>
+          <t>93,84; 96,84</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>88,47; 92,35</t>
+          <t>88,45; 92,23</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>93,92; 96,25</t>
+          <t>93,95; 96,21</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>94,06; 96,39</t>
+          <t>93,96; 96,4</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>92,74; 95,34</t>
+          <t>92,65; 95,36</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>87,43; 91,02</t>
+          <t>87,48; 90,91</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>92,16%</t>
+          <t>89,94%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>91,4%</t>
+          <t>91,2%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>91,82%</t>
+          <t>90,58%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>90,16; 93,78</t>
+          <t>90,02; 93,77</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>92,88; 96,1</t>
+          <t>93,07; 96,09</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>89,59; 93,24</t>
+          <t>89,61; 93,32</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>89,43; 96,46</t>
+          <t>87,47; 91,83</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>91,53; 94,75</t>
+          <t>91,46; 94,83</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>93,02; 96,0</t>
+          <t>93,08; 95,94</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>91,25; 94,56</t>
+          <t>91,51; 94,56</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>89,73; 92,9</t>
+          <t>89,47; 92,82</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>91,32; 93,74</t>
+          <t>91,34; 93,87</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>93,55; 95,63</t>
+          <t>93,56; 95,67</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>91,01; 93,42</t>
+          <t>91,11; 93,5</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>90,22; 94,65</t>
+          <t>89,16; 91,77</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>80,48%</t>
+          <t>81,36%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>88,68%</t>
+          <t>85,17%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>85,15%</t>
+          <t>83,28%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>90,24; 94,47</t>
+          <t>90,34; 94,45</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>87,07; 91,9</t>
+          <t>87,21; 91,76</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>86,15; 90,82</t>
+          <t>86,05; 90,83</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>76,86; 83,64</t>
+          <t>78,06; 84,37</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>91,95; 95,48</t>
+          <t>91,96; 95,36</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>90,8; 94,68</t>
+          <t>90,54; 94,44</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>91,5; 95,05</t>
+          <t>91,51; 94,99</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>84,57; 94,37</t>
+          <t>82,87; 87,28</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>91,66; 94,53</t>
+          <t>91,8; 94,4</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>89,7; 92,72</t>
+          <t>89,71; 92,77</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>89,53; 92,57</t>
+          <t>89,49; 92,46</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>82,26; 90,24</t>
+          <t>81,1; 85,13</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>88,59%</t>
+          <t>88,25%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>83,39%</t>
+          <t>88,63%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>85,78%</t>
+          <t>88,45%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>90,5; 94,08</t>
+          <t>90,7; 94,02</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>91,73; 95,06</t>
+          <t>91,68; 95,01</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>92,07; 95,27</t>
+          <t>92,34; 95,3</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>85,83; 90,81</t>
+          <t>85,72; 90,55</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>93,34; 96,09</t>
+          <t>93,29; 96,06</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,2; 95,11</t>
+          <t>91,9; 95,05</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>92,89; 95,7</t>
+          <t>92,94; 95,73</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>67,65; 89,57</t>
+          <t>86,73; 90,14</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>92,63; 94,75</t>
+          <t>92,64; 94,86</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>92,38; 94,69</t>
+          <t>92,39; 94,68</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>93,13; 95,25</t>
+          <t>92,96; 95,22</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>75,11; 89,23</t>
+          <t>87,05; 89,73</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>88,08%</t>
+          <t>87,17%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>88,17%</t>
+          <t>88,96%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>88,13%</t>
+          <t>88,09%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>91,92; 93,75</t>
+          <t>91,94; 93,78</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>92,29; 94,22</t>
+          <t>92,41; 94,13</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>90,77; 92,78</t>
+          <t>90,76; 92,69</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>86,42; 90,65</t>
+          <t>85,85; 88,45</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>93,47; 95,01</t>
+          <t>93,53; 95,16</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>93,27; 94,98</t>
+          <t>93,29; 94,94</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>93,22; 94,87</t>
+          <t>93,23; 94,79</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>82,61; 90,53</t>
+          <t>87,98; 89,85</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>92,91; 94,19</t>
+          <t>93,01; 94,18</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>93,13; 94,38</t>
+          <t>93,17; 94,35</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>92,33; 93,49</t>
+          <t>92,29; 93,51</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>85,02; 89,71</t>
+          <t>87,37; 88,83</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>559908</t>
+          <t>609046</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>612217</t>
+          <t>662384</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1172125</t>
+          <t>1271429</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>646679; 669080</t>
+          <t>647027; 669480</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>654416; 680223</t>
+          <t>655314; 678897</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>609275; 637593</t>
+          <t>609526; 637816</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>539841; 576334</t>
+          <t>586640; 625476</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>644362; 666177</t>
+          <t>645766; 667048</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>654042; 676330</t>
+          <t>653742; 676429</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>629028; 650538</t>
+          <t>629620; 649750</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>597528; 623682</t>
+          <t>648066; 675790</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1298373; 1330471</t>
+          <t>1298759; 1330005</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1317278; 1349962</t>
+          <t>1315966; 1350151</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>1247298; 1282180</t>
+          <t>1245981; 1282473</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1146050; 1193155</t>
+          <t>1245288; 1294108</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1099339</t>
+          <t>943395</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>875668</t>
+          <t>976620</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1975009</t>
+          <t>1920015</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>867181; 901955</t>
+          <t>865775; 901842</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>945450; 978207</t>
+          <t>947451; 978181</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>915115; 952413</t>
+          <t>915359; 953237</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1066751; 1150667</t>
+          <t>917439; 963230</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>886399; 917596</t>
+          <t>885738; 918360</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>959216; 989970</t>
+          <t>959811; 989321</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>951630; 986224</t>
+          <t>954362; 986146</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>859740; 890056</t>
+          <t>958074; 993978</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1762637; 1809281</t>
+          <t>1763087; 1811873</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1917023; 1959671</t>
+          <t>1917179; 1960397</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1878739; 1928456</t>
+          <t>1880796; 1930240</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1940538; 2035885</t>
+          <t>1889869; 1945358</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>567105</t>
+          <t>653413</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>827709</t>
+          <t>691819</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1394814</t>
+          <t>1345231</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>612288; 641008</t>
+          <t>612996; 640872</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>659674; 696243</t>
+          <t>660717; 695219</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>652543; 687851</t>
+          <t>651733; 687961</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>541605; 589385</t>
+          <t>626866; 677519</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>627742; 651862</t>
+          <t>627793; 651022</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>702914; 732977</t>
+          <t>700910; 731125</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>718251; 746125</t>
+          <t>718398; 745653</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>789380; 880842</t>
+          <t>673096; 708916</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1247667; 1286792</t>
+          <t>1249626; 1285007</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1374060; 1420271</t>
+          <t>1374184; 1420961</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1380997; 1427791</t>
+          <t>1380369; 1426164</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1347492; 1478153</t>
+          <t>1309960; 1375092</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>821120</t>
+          <t>873682</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>913091</t>
+          <t>991860</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>1734211</t>
+          <t>1865543</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>851933; 885600</t>
+          <t>853751; 885017</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>868484; 900059</t>
+          <t>868038; 899624</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>860522; 890450</t>
+          <t>863033; 890743</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>795524; 841667</t>
+          <t>848709; 896523</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>969411; 997967</t>
+          <t>968938; 997682</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>968090; 998634</t>
+          <t>964899; 997979</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>968559; 997820</t>
+          <t>969095; 998169</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>740764; 980732</t>
+          <t>970598; 1008681</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1834030; 1875982</t>
+          <t>1834302; 1878128</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1844599; 1890801</t>
+          <t>1844891; 1890590</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1841414; 1883372</t>
+          <t>1838209; 1882895</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1518465; 1803922</t>
+          <t>1835959; 1892529</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3047473</t>
+          <t>3079536</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>3228685</t>
+          <t>3322683</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>6276158</t>
+          <t>6402219</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>3010865; 3070960</t>
+          <t>3011724; 3071974</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3161665; 3227948</t>
+          <t>3165996; 3224637</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3074831; 3142986</t>
+          <t>3074343; 3139692</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2989897; 3136156</t>
+          <t>3032838; 3124665</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>3157344; 3209454</t>
+          <t>3159450; 3214503</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3313344; 3374125</t>
+          <t>3314081; 3372541</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>3301378; 3359736</t>
+          <t>3301831; 3356938</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>3024967; 3314975</t>
+          <t>3286012; 3355599</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>6182195; 6267216</t>
+          <t>6188622; 6266671</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>6498776; 6586109</t>
+          <t>6501487; 6583665</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>6397489; 6478012</t>
+          <t>6394732; 6479156</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>6055024; 6388820</t>
+          <t>6349366; 6455660</t>
         </is>
       </c>
     </row>
